--- a/data/raw/sales/Week 28/Tonor/Vendor Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 28/Tonor/Vendor Sales (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,86 +413,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>category_l0</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>category_l1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>category_l2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Sale</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ShippedUnits</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ShippedRevenue</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>CustomerReturns</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>WindowStart</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>WindowEnd</t>
         </is>
@@ -546,10 +534,10 @@
         <v>38</v>
       </c>
       <c r="I2" t="n">
-        <v>52259.16</v>
+        <v>52547.3</v>
       </c>
       <c r="J2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -572,7 +560,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -615,7 +603,7 @@
         <v>17238.96</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -638,7 +626,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -675,19 +663,19 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>33593.22</v>
+        <v>35880.5</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -704,7 +692,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -770,7 +758,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -807,10 +795,10 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>9910.16</v>
+        <v>11604.22</v>
       </c>
       <c r="J6" t="n">
         <v>7</v>
@@ -836,7 +824,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -902,7 +890,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -968,7 +956,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -1011,7 +999,7 @@
         <v>31151.71</v>
       </c>
       <c r="J9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1034,7 +1022,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -1071,13 +1059,13 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>27338.14</v>
+        <v>34962.73</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1100,7 +1088,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1154,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1197,7 @@
         <v>2372.03</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1232,19 +1220,19 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FBA79113</t>
+          <t>FBA79111</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1254,28 +1242,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TC310</t>
+          <t>TD510</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tripod - RGB</t>
+          <t>USB/XLR Mic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>6183.91</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1298,19 +1286,19 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FBA79116</t>
+          <t>FBA79113</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1320,7 +1308,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TC-777 PRO</t>
+          <t>TC310</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1335,19 +1323,19 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>21212.71</v>
+        <v>8301.709999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1364,19 +1352,19 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FBA79114</t>
+          <t>FBA79116</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1386,7 +1374,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TC310+</t>
+          <t>TC-777 PRO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1396,24 +1384,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Boom Arm Kit - USB - RGB</t>
+          <t>Tripod - RGB</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>2456.78</v>
+        <v>24770.33</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1430,19 +1418,19 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FBA79585</t>
+          <t>FBA79114</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1452,29 +1440,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T20LP</t>
+          <t>TC310+</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Low Profile Boom Arm</t>
+          <t>Boom Arm Kit - USB - RGB</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2456.78</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>3515.25</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
@@ -1496,19 +1484,19 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FBA79696</t>
+          <t>FBA79585</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1518,28 +1506,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TD310+</t>
+          <t>T20LP</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hand held Mic + Boom Arm</t>
+          <t>Low Profile Boom Arm</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>5421.19</v>
+        <v>3515.25</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1562,19 +1550,19 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FBA79697</t>
+          <t>FBA79696</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1584,7 +1572,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TD310</t>
+          <t>TD310+</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1594,24 +1582,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hand held Mic + Stand</t>
+          <t>Hand held Mic + Boom Arm</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>27615.23</v>
+        <v>7284.75</v>
       </c>
       <c r="J18" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1628,19 +1616,19 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FBA79577</t>
+          <t>FBA79697</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1650,51 +1638,117 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TM310</t>
+          <t>TD310</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wired</t>
+          <t>Hand held Mic + Stand</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
+        <v>22</v>
+      </c>
+      <c r="I19" t="n">
+        <v>32697.44</v>
+      </c>
+      <c r="J19" t="n">
+        <v>22</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1p Sales</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>28</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B0CSCT63BL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FBA79577</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TM310</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Conference Microphone</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Wired</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>3896.62</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>1p Sales</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>28</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1p Sales</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>28</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>

--- a/data/raw/sales/Week 28/Tonor/Vendor Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 28/Tonor/Vendor Sales (SP-API).xlsx
@@ -1401,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
